--- a/data/trans_bre/P16A_n_R3-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R3-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,89</t>
+          <t>-0,96; 0,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,16</t>
+          <t>1,48; 5,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,9</t>
+          <t>0,98; 4,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,18</t>
+          <t>1,0; 5,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,96; 221,02</t>
+          <t>-76,62; 217,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,82; 675,14</t>
+          <t>59,7; 626,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,27; 314,82</t>
+          <t>27,48; 346,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,82; 130,57</t>
+          <t>13,57; 118,54</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,12</t>
+          <t>-0,56; 1,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,54</t>
+          <t>2,31; 5,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,37</t>
+          <t>0,41; 3,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,3</t>
+          <t>4,01; 8,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 242,2</t>
+          <t>-28,01; 217,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>115,95; 833,3</t>
+          <t>118,14; 806,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,37; 320,05</t>
+          <t>11,52; 302,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,69; 411,49</t>
+          <t>88,85; 431,06</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,53</t>
+          <t>1,18; 4,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,23</t>
+          <t>-0,71; 3,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,86</t>
+          <t>0,36; 3,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 4,23</t>
+          <t>-1,72; 4,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,81; 547,54</t>
+          <t>44,68; 581,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 220,52</t>
+          <t>-21,58; 244,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 327,29</t>
+          <t>6,05; 300,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 135,29</t>
+          <t>-32,82; 135,56</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,46</t>
+          <t>-0,14; 2,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,51</t>
+          <t>1,66; 5,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,68</t>
+          <t>2,37; 5,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,8</t>
+          <t>3,07; 7,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 175,26</t>
+          <t>-12,99; 181,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,21; 334,4</t>
+          <t>42,24; 336,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>126,7; 802,56</t>
+          <t>113,67; 755,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,3; 173,67</t>
+          <t>51,42; 179,26</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,81</t>
+          <t>0,42; 1,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,09</t>
+          <t>2,3; 4,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,51</t>
+          <t>1,83; 3,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,62</t>
+          <t>2,72; 5,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,91; 147,9</t>
+          <t>21,21; 149,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>97,03; 282,46</t>
+          <t>104,48; 277,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,56; 252,42</t>
+          <t>90,34; 261,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>56,87; 152,43</t>
+          <t>56,59; 153,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A_n_R3-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R3-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>4,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>70,85%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,88</t>
+          <t>-1,08; 0,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,02</t>
+          <t>1,74; 5,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,81</t>
+          <t>0,87; 4,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,91</t>
+          <t>1,89; 6,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-76,62; 217,62</t>
+          <t>-76,85; 213,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,7; 626,39</t>
+          <t>83,02; 726,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,48; 346,6</t>
+          <t>22,49; 318,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,57; 118,54</t>
+          <t>23,2; 132,67</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,86</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>167,41%</t>
+          <t>117,53%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,98</t>
+          <t>-0,53; 2,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,68</t>
+          <t>2,28; 5,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,33</t>
+          <t>0,43; 3,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 8,29</t>
+          <t>3,14; 6,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,01; 217,09</t>
+          <t>-27,46; 228,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>118,14; 806,11</t>
+          <t>101,29; 705,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,52; 302,21</t>
+          <t>15,65; 341,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88,85; 431,06</t>
+          <t>57,0; 194,13</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>3,38</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,45</t>
+          <t>1,03; 4,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,24</t>
+          <t>-0,71; 3,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,88</t>
+          <t>0,5; 3,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 4,21</t>
+          <t>1,33; 5,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,68; 581,02</t>
+          <t>40,12; 589,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 244,15</t>
+          <t>-23,8; 236,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 300,1</t>
+          <t>6,53; 318,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 135,56</t>
+          <t>28,77; 180,42</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>102,61%</t>
+          <t>114,04%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,55</t>
+          <t>-0,29; 2,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,44</t>
+          <t>1,57; 5,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,51</t>
+          <t>2,19; 5,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 7,87</t>
+          <t>4,11; 8,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 181,29</t>
+          <t>-13,77; 160,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,24; 336,4</t>
+          <t>43,05; 321,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>113,67; 755,86</t>
+          <t>117,32; 736,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,42; 179,26</t>
+          <t>67,91; 185,76</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>101,37%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,8</t>
+          <t>0,46; 1,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,08</t>
+          <t>2,31; 4,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,54</t>
+          <t>1,89; 3,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,72</t>
+          <t>3,82; 5,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,21; 149,55</t>
+          <t>22,95; 147,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>104,48; 277,36</t>
+          <t>103,59; 291,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,34; 261,09</t>
+          <t>89,32; 254,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>56,59; 153,74</t>
+          <t>71,61; 134,68</t>
         </is>
       </c>
     </row>
